--- a/bus_booking1.xlsx
+++ b/bus_booking1.xlsx
@@ -1,23 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\front2\OneDrive\ドキュメント\bus-booking\Xe bus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{922C1B88-BC07-4B95-A556-D80D7227227E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90A2D261-C059-42EC-9815-987336AB052F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{42734889-29B0-4E0D-9607-DDF20B1FC993}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{42734889-29B0-4E0D-9607-DDF20B1FC993}"/>
   </bookViews>
   <sheets>
     <sheet name="6-7" sheetId="2" r:id="rId1"/>
     <sheet name="7-10" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'6-7'!$B$1:$D$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'7-10'!$A$1:$D$41</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -131,7 +130,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -157,15 +156,6 @@
     </font>
     <font>
       <b/>
-      <sz val="20"/>
-      <color theme="1"/>
-      <name val="Yu Gothic"/>
-      <family val="3"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="18"/>
       <color theme="1"/>
       <name val="Yu Gothic"/>
@@ -174,8 +164,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="14"/>
+      <sz val="18"/>
       <color theme="1"/>
       <name val="Yu Gothic"/>
       <family val="3"/>
@@ -538,7 +527,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
@@ -549,102 +538,105 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="20" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="20" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -927,244 +919,243 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19864BDF-6C88-4C7B-8208-20D7363459CB}">
   <dimension ref="B1:D44"/>
-  <sheetFormatPr defaultRowHeight="24"/>
+  <sheetFormatPr defaultRowHeight="30"/>
   <cols>
-    <col min="1" max="1" width="3.25" style="22" customWidth="1"/>
-    <col min="2" max="2" width="9" style="22"/>
-    <col min="3" max="3" width="56.5" style="22" customWidth="1"/>
-    <col min="4" max="4" width="55.75" style="22" customWidth="1"/>
-    <col min="5" max="16384" width="9" style="22"/>
+    <col min="1" max="1" width="3.25" style="5" customWidth="1"/>
+    <col min="2" max="2" width="9" style="5"/>
+    <col min="3" max="4" width="42.625" style="5" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:4">
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="6" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="2:4" ht="9.75" customHeight="1" thickBot="1">
-      <c r="D2" s="4"/>
+      <c r="D2" s="7"/>
     </row>
     <row r="3" spans="2:4" ht="24.95" customHeight="1">
-      <c r="B3" s="23"/>
-      <c r="C3" s="5" t="s">
+      <c r="B3" s="8"/>
+      <c r="C3" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="10" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" spans="2:4" ht="10.5" customHeight="1">
-      <c r="B4" s="24"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="26"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="13"/>
     </row>
     <row r="5" spans="2:4">
-      <c r="B5" s="29">
+      <c r="B5" s="14">
         <v>0.25347222222222221</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="14"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="16"/>
     </row>
     <row r="6" spans="2:4">
-      <c r="B6" s="29"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="15"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="18"/>
     </row>
     <row r="7" spans="2:4">
-      <c r="B7" s="29"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="15"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="18"/>
     </row>
     <row r="8" spans="2:4">
-      <c r="B8" s="29"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="15"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="18"/>
     </row>
     <row r="9" spans="2:4">
-      <c r="B9" s="29"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="15"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="18"/>
     </row>
     <row r="10" spans="2:4">
-      <c r="B10" s="29"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="15"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="18"/>
     </row>
     <row r="11" spans="2:4">
-      <c r="B11" s="29"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="15"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="18"/>
     </row>
     <row r="12" spans="2:4">
-      <c r="B12" s="29"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="15"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="18"/>
     </row>
     <row r="13" spans="2:4">
-      <c r="B13" s="29"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="15"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="18"/>
     </row>
     <row r="14" spans="2:4">
-      <c r="B14" s="29"/>
+      <c r="B14" s="14"/>
       <c r="C14" s="19"/>
-      <c r="D14" s="16"/>
+      <c r="D14" s="20"/>
     </row>
     <row r="15" spans="2:4">
-      <c r="B15" s="29">
+      <c r="B15" s="14">
         <v>0.2638888888888889</v>
       </c>
-      <c r="C15" s="17"/>
-      <c r="D15" s="14"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="16"/>
     </row>
     <row r="16" spans="2:4">
-      <c r="B16" s="29"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="15"/>
+      <c r="B16" s="14"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="18"/>
     </row>
     <row r="17" spans="2:4">
-      <c r="B17" s="29"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="15"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="18"/>
     </row>
     <row r="18" spans="2:4">
-      <c r="B18" s="29"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="15"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="18"/>
     </row>
     <row r="19" spans="2:4">
-      <c r="B19" s="29"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="15"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="18"/>
     </row>
     <row r="20" spans="2:4">
-      <c r="B20" s="29"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="15"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="18"/>
     </row>
     <row r="21" spans="2:4">
-      <c r="B21" s="29"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="15"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="18"/>
     </row>
     <row r="22" spans="2:4">
-      <c r="B22" s="29"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="15"/>
+      <c r="B22" s="14"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="18"/>
     </row>
     <row r="23" spans="2:4">
-      <c r="B23" s="29"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="15"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="18"/>
     </row>
     <row r="24" spans="2:4">
-      <c r="B24" s="29"/>
+      <c r="B24" s="14"/>
       <c r="C24" s="19"/>
-      <c r="D24" s="16"/>
+      <c r="D24" s="20"/>
     </row>
     <row r="25" spans="2:4">
-      <c r="B25" s="29">
+      <c r="B25" s="14">
         <v>0.27777777777777779</v>
       </c>
-      <c r="C25" s="17"/>
-      <c r="D25" s="14"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="16"/>
     </row>
     <row r="26" spans="2:4">
-      <c r="B26" s="29"/>
-      <c r="C26" s="18"/>
-      <c r="D26" s="15"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="18"/>
     </row>
     <row r="27" spans="2:4">
-      <c r="B27" s="29"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="15"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="18"/>
     </row>
     <row r="28" spans="2:4">
-      <c r="B28" s="29"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="15"/>
+      <c r="B28" s="14"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="18"/>
     </row>
     <row r="29" spans="2:4">
-      <c r="B29" s="29"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="15"/>
+      <c r="B29" s="14"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="18"/>
     </row>
     <row r="30" spans="2:4">
-      <c r="B30" s="29"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="15"/>
+      <c r="B30" s="14"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="18"/>
     </row>
     <row r="31" spans="2:4">
-      <c r="B31" s="29"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="15"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="18"/>
     </row>
     <row r="32" spans="2:4">
-      <c r="B32" s="29"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="15"/>
+      <c r="B32" s="14"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="18"/>
     </row>
     <row r="33" spans="2:4">
-      <c r="B33" s="29"/>
-      <c r="C33" s="18"/>
-      <c r="D33" s="15"/>
+      <c r="B33" s="14"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="18"/>
     </row>
     <row r="34" spans="2:4">
-      <c r="B34" s="29"/>
+      <c r="B34" s="14"/>
       <c r="C34" s="19"/>
-      <c r="D34" s="16"/>
+      <c r="D34" s="20"/>
     </row>
     <row r="35" spans="2:4">
-      <c r="B35" s="29">
+      <c r="B35" s="14">
         <v>0.29166666666666669</v>
       </c>
-      <c r="C35" s="17"/>
-      <c r="D35" s="14"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="16"/>
     </row>
     <row r="36" spans="2:4">
-      <c r="B36" s="29"/>
-      <c r="C36" s="18"/>
-      <c r="D36" s="15"/>
+      <c r="B36" s="14"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="18"/>
     </row>
     <row r="37" spans="2:4">
-      <c r="B37" s="29"/>
-      <c r="C37" s="18"/>
-      <c r="D37" s="15"/>
+      <c r="B37" s="14"/>
+      <c r="C37" s="17"/>
+      <c r="D37" s="18"/>
     </row>
     <row r="38" spans="2:4">
-      <c r="B38" s="29"/>
-      <c r="C38" s="18"/>
-      <c r="D38" s="15"/>
+      <c r="B38" s="14"/>
+      <c r="C38" s="17"/>
+      <c r="D38" s="18"/>
     </row>
     <row r="39" spans="2:4">
-      <c r="B39" s="29"/>
-      <c r="C39" s="18"/>
-      <c r="D39" s="15"/>
+      <c r="B39" s="14"/>
+      <c r="C39" s="17"/>
+      <c r="D39" s="18"/>
     </row>
     <row r="40" spans="2:4">
-      <c r="B40" s="29"/>
-      <c r="C40" s="18"/>
-      <c r="D40" s="15"/>
+      <c r="B40" s="14"/>
+      <c r="C40" s="17"/>
+      <c r="D40" s="18"/>
     </row>
     <row r="41" spans="2:4">
-      <c r="B41" s="29"/>
-      <c r="C41" s="18"/>
-      <c r="D41" s="15"/>
+      <c r="B41" s="14"/>
+      <c r="C41" s="17"/>
+      <c r="D41" s="18"/>
     </row>
     <row r="42" spans="2:4">
-      <c r="B42" s="29"/>
-      <c r="C42" s="18"/>
-      <c r="D42" s="15"/>
+      <c r="B42" s="14"/>
+      <c r="C42" s="17"/>
+      <c r="D42" s="18"/>
     </row>
     <row r="43" spans="2:4">
-      <c r="B43" s="29"/>
-      <c r="C43" s="18"/>
-      <c r="D43" s="15"/>
-    </row>
-    <row r="44" spans="2:4" ht="24.75" thickBot="1">
-      <c r="B44" s="30"/>
-      <c r="C44" s="27"/>
-      <c r="D44" s="28"/>
+      <c r="B43" s="14"/>
+      <c r="C43" s="17"/>
+      <c r="D43" s="18"/>
+    </row>
+    <row r="44" spans="2:4" ht="30.75" thickBot="1">
+      <c r="B44" s="21"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1175,7 +1166,7 @@
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="72" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="90" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1199,279 +1190,279 @@
       <c r="D2" s="2"/>
     </row>
     <row r="3" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A3" s="45" t="s">
+      <c r="A3" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="47" t="s">
+      <c r="B3" s="25"/>
+      <c r="C3" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="8"/>
+      <c r="D3" s="27"/>
     </row>
     <row r="4" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A4" s="46"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="10"/>
+      <c r="A4" s="28"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="30"/>
     </row>
     <row r="5" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A5" s="46"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="10"/>
+      <c r="A5" s="28"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="30"/>
     </row>
     <row r="6" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A6" s="46"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="10"/>
+      <c r="A6" s="28"/>
+      <c r="B6" s="29"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="30"/>
     </row>
     <row r="7" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A7" s="46"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="48"/>
-      <c r="D7" s="10"/>
+      <c r="A7" s="28"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="30"/>
     </row>
     <row r="8" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A8" s="46"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="10"/>
+      <c r="A8" s="28"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="30"/>
     </row>
     <row r="9" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A9" s="46"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="10"/>
+      <c r="A9" s="28"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="30"/>
     </row>
     <row r="10" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A10" s="46"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="48"/>
-      <c r="D10" s="10"/>
+      <c r="A10" s="28"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="30"/>
     </row>
     <row r="11" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A11" s="46"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="48"/>
-      <c r="D11" s="10"/>
+      <c r="A11" s="28"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="30"/>
     </row>
     <row r="12" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A12" s="46"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="48"/>
-      <c r="D12" s="10"/>
+      <c r="A12" s="28"/>
+      <c r="B12" s="29"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="30"/>
     </row>
     <row r="13" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A13" s="46"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="48"/>
-      <c r="D13" s="12"/>
+      <c r="A13" s="28"/>
+      <c r="B13" s="31"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="32"/>
     </row>
     <row r="14" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A14" s="46" t="s">
+      <c r="A14" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="B14" s="13"/>
-      <c r="C14" s="48" t="s">
+      <c r="B14" s="33"/>
+      <c r="C14" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D14" s="14"/>
+      <c r="D14" s="34"/>
     </row>
     <row r="15" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A15" s="46"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="15"/>
+      <c r="A15" s="28"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="35"/>
     </row>
     <row r="16" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A16" s="46"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="48"/>
-      <c r="D16" s="15"/>
+      <c r="A16" s="28"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="35"/>
     </row>
     <row r="17" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A17" s="46"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="48"/>
-      <c r="D17" s="15"/>
+      <c r="A17" s="28"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="35"/>
     </row>
     <row r="18" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A18" s="46"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="48"/>
-      <c r="D18" s="15"/>
+      <c r="A18" s="28"/>
+      <c r="B18" s="29"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="35"/>
     </row>
     <row r="19" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A19" s="46"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="48"/>
-      <c r="D19" s="15"/>
+      <c r="A19" s="28"/>
+      <c r="B19" s="29"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="35"/>
     </row>
     <row r="20" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A20" s="46"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="48"/>
-      <c r="D20" s="15"/>
+      <c r="A20" s="28"/>
+      <c r="B20" s="29"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="35"/>
     </row>
     <row r="21" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A21" s="46"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="48"/>
-      <c r="D21" s="15"/>
+      <c r="A21" s="28"/>
+      <c r="B21" s="29"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="35"/>
     </row>
     <row r="22" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A22" s="46"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="48"/>
-      <c r="D22" s="15"/>
+      <c r="A22" s="28"/>
+      <c r="B22" s="29"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="35"/>
     </row>
     <row r="23" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A23" s="46"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="48"/>
-      <c r="D23" s="15"/>
+      <c r="A23" s="28"/>
+      <c r="B23" s="29"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="35"/>
     </row>
     <row r="24" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A24" s="46"/>
-      <c r="B24" s="11"/>
-      <c r="C24" s="48"/>
-      <c r="D24" s="16"/>
+      <c r="A24" s="28"/>
+      <c r="B24" s="31"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="36"/>
     </row>
     <row r="25" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A25" s="46" t="s">
+      <c r="A25" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="B25" s="17"/>
-      <c r="C25" s="48" t="s">
+      <c r="B25" s="37"/>
+      <c r="C25" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D25" s="15"/>
+      <c r="D25" s="35"/>
     </row>
     <row r="26" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A26" s="46"/>
-      <c r="B26" s="18"/>
-      <c r="C26" s="48"/>
-      <c r="D26" s="15"/>
+      <c r="A26" s="28"/>
+      <c r="B26" s="38"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="35"/>
     </row>
     <row r="27" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A27" s="46"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="48"/>
-      <c r="D27" s="15"/>
+      <c r="A27" s="28"/>
+      <c r="B27" s="38"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="35"/>
     </row>
     <row r="28" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A28" s="46"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="48"/>
-      <c r="D28" s="15"/>
+      <c r="A28" s="28"/>
+      <c r="B28" s="38"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="35"/>
     </row>
     <row r="29" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A29" s="46"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="48"/>
-      <c r="D29" s="15"/>
+      <c r="A29" s="28"/>
+      <c r="B29" s="38"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="35"/>
     </row>
     <row r="30" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A30" s="46"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="48"/>
-      <c r="D30" s="15"/>
+      <c r="A30" s="28"/>
+      <c r="B30" s="38"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="35"/>
     </row>
     <row r="31" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A31" s="46"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="48"/>
-      <c r="D31" s="15"/>
+      <c r="A31" s="28"/>
+      <c r="B31" s="38"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="35"/>
     </row>
     <row r="32" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A32" s="46"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="48"/>
-      <c r="D32" s="15"/>
+      <c r="A32" s="28"/>
+      <c r="B32" s="38"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="35"/>
     </row>
     <row r="33" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A33" s="46"/>
-      <c r="B33" s="18"/>
-      <c r="C33" s="48"/>
-      <c r="D33" s="15"/>
+      <c r="A33" s="28"/>
+      <c r="B33" s="38"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="35"/>
     </row>
     <row r="34" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A34" s="46"/>
-      <c r="B34" s="18"/>
-      <c r="C34" s="48"/>
-      <c r="D34" s="15"/>
+      <c r="A34" s="28"/>
+      <c r="B34" s="38"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="35"/>
     </row>
     <row r="35" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A35" s="46"/>
-      <c r="B35" s="19"/>
-      <c r="C35" s="48"/>
-      <c r="D35" s="15"/>
+      <c r="A35" s="28"/>
+      <c r="B35" s="39"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="35"/>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="31"/>
-      <c r="B36" s="33" t="s">
+      <c r="A36" s="14"/>
+      <c r="B36" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="C36" s="35" t="s">
+      <c r="C36" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="D36" s="36"/>
+      <c r="D36" s="42"/>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="31"/>
-      <c r="B37" s="34"/>
-      <c r="C37" s="37"/>
-      <c r="D37" s="38"/>
+      <c r="A37" s="14"/>
+      <c r="B37" s="43"/>
+      <c r="C37" s="44"/>
+      <c r="D37" s="45"/>
     </row>
     <row r="38" spans="1:4" ht="24" customHeight="1">
-      <c r="A38" s="31"/>
-      <c r="B38" s="20" t="s">
+      <c r="A38" s="14"/>
+      <c r="B38" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="C38" s="39" t="s">
+      <c r="C38" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="D38" s="40"/>
+      <c r="D38" s="48"/>
     </row>
     <row r="39" spans="1:4" ht="24" customHeight="1">
-      <c r="A39" s="31"/>
-      <c r="B39" s="20" t="s">
+      <c r="A39" s="14"/>
+      <c r="B39" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="C39" s="41"/>
-      <c r="D39" s="42"/>
+      <c r="C39" s="49"/>
+      <c r="D39" s="50"/>
     </row>
     <row r="40" spans="1:4" ht="24" customHeight="1">
-      <c r="A40" s="31"/>
-      <c r="B40" s="9"/>
-      <c r="C40" s="41" t="s">
+      <c r="A40" s="14"/>
+      <c r="B40" s="29"/>
+      <c r="C40" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="D40" s="42"/>
-    </row>
-    <row r="41" spans="1:4" ht="24.75" thickBot="1">
-      <c r="A41" s="32"/>
-      <c r="B41" s="21"/>
-      <c r="C41" s="43"/>
-      <c r="D41" s="44"/>
+      <c r="D40" s="50"/>
+    </row>
+    <row r="41" spans="1:4" ht="30.75" thickBot="1">
+      <c r="A41" s="21"/>
+      <c r="B41" s="51"/>
+      <c r="C41" s="52"/>
+      <c r="D41" s="53"/>
     </row>
     <row r="43" spans="1:4">
       <c r="D43" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A36:A41"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:D37"/>
+    <mergeCell ref="C38:D39"/>
+    <mergeCell ref="C40:D41"/>
     <mergeCell ref="A3:A13"/>
     <mergeCell ref="C3:C13"/>
     <mergeCell ref="A14:A24"/>
     <mergeCell ref="C14:C24"/>
     <mergeCell ref="A25:A35"/>
     <mergeCell ref="C25:C35"/>
-    <mergeCell ref="A36:A41"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:D37"/>
-    <mergeCell ref="C38:D39"/>
-    <mergeCell ref="C40:D41"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.70866141732283472" right="0.31496062992125984" top="0.74803149606299213" bottom="0.55118110236220474" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/bus_booking1.xlsx
+++ b/bus_booking1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\front2\OneDrive\ドキュメント\bus-booking\Xe bus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90A2D261-C059-42EC-9815-987336AB052F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56552EC4-8DA1-424B-B179-DA33EC2A2C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{42734889-29B0-4E0D-9607-DDF20B1FC993}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{42734889-29B0-4E0D-9607-DDF20B1FC993}"/>
   </bookViews>
   <sheets>
     <sheet name="6-7" sheetId="2" r:id="rId1"/>
@@ -156,7 +156,7 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Yu Gothic"/>
       <family val="3"/>
@@ -164,7 +164,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="18"/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Yu Gothic"/>
       <family val="3"/>
@@ -538,44 +538,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="20" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -588,6 +550,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
@@ -598,6 +563,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -630,6 +598,9 @@
     </xf>
     <xf numFmtId="20" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="20" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -638,6 +609,35 @@
     <xf numFmtId="20" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -919,243 +919,243 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19864BDF-6C88-4C7B-8208-20D7363459CB}">
   <dimension ref="B1:D44"/>
-  <sheetFormatPr defaultRowHeight="30"/>
+  <sheetFormatPr defaultRowHeight="24"/>
   <cols>
-    <col min="1" max="1" width="3.25" style="5" customWidth="1"/>
-    <col min="2" max="2" width="9" style="5"/>
-    <col min="3" max="4" width="42.625" style="5" customWidth="1"/>
-    <col min="5" max="16384" width="9" style="5"/>
+    <col min="1" max="1" width="3.25" style="37" customWidth="1"/>
+    <col min="2" max="2" width="9" style="37"/>
+    <col min="3" max="4" width="42.625" style="37" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="37"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:4">
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="38" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="2:4" ht="9.75" customHeight="1" thickBot="1">
-      <c r="D2" s="7"/>
+      <c r="D2" s="39"/>
     </row>
     <row r="3" spans="2:4" ht="24.95" customHeight="1">
-      <c r="B3" s="8"/>
-      <c r="C3" s="9" t="s">
+      <c r="B3" s="40"/>
+      <c r="C3" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="42" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" spans="2:4" ht="10.5" customHeight="1">
-      <c r="B4" s="11"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="13"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="45"/>
     </row>
     <row r="5" spans="2:4">
-      <c r="B5" s="14">
+      <c r="B5" s="21">
         <v>0.25347222222222221</v>
       </c>
-      <c r="C5" s="15"/>
-      <c r="D5" s="16"/>
+      <c r="C5" s="46"/>
+      <c r="D5" s="47"/>
     </row>
     <row r="6" spans="2:4">
-      <c r="B6" s="14"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="18"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="49"/>
     </row>
     <row r="7" spans="2:4">
-      <c r="B7" s="14"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="18"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="49"/>
     </row>
     <row r="8" spans="2:4">
-      <c r="B8" s="14"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="18"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="49"/>
     </row>
     <row r="9" spans="2:4">
-      <c r="B9" s="14"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="18"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="49"/>
     </row>
     <row r="10" spans="2:4">
-      <c r="B10" s="14"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="18"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="49"/>
     </row>
     <row r="11" spans="2:4">
-      <c r="B11" s="14"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="18"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="49"/>
     </row>
     <row r="12" spans="2:4">
-      <c r="B12" s="14"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="18"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="48"/>
+      <c r="D12" s="49"/>
     </row>
     <row r="13" spans="2:4">
-      <c r="B13" s="14"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="18"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="49"/>
     </row>
     <row r="14" spans="2:4">
-      <c r="B14" s="14"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="20"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="50"/>
+      <c r="D14" s="51"/>
     </row>
     <row r="15" spans="2:4">
-      <c r="B15" s="14">
+      <c r="B15" s="21">
         <v>0.2638888888888889</v>
       </c>
-      <c r="C15" s="15"/>
-      <c r="D15" s="16"/>
+      <c r="C15" s="46"/>
+      <c r="D15" s="47"/>
     </row>
     <row r="16" spans="2:4">
-      <c r="B16" s="14"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="18"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="48"/>
+      <c r="D16" s="49"/>
     </row>
     <row r="17" spans="2:4">
-      <c r="B17" s="14"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="18"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="48"/>
+      <c r="D17" s="49"/>
     </row>
     <row r="18" spans="2:4">
-      <c r="B18" s="14"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="18"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="48"/>
+      <c r="D18" s="49"/>
     </row>
     <row r="19" spans="2:4">
-      <c r="B19" s="14"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="18"/>
+      <c r="B19" s="21"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="49"/>
     </row>
     <row r="20" spans="2:4">
-      <c r="B20" s="14"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="18"/>
+      <c r="B20" s="21"/>
+      <c r="C20" s="48"/>
+      <c r="D20" s="49"/>
     </row>
     <row r="21" spans="2:4">
-      <c r="B21" s="14"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="18"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="48"/>
+      <c r="D21" s="49"/>
     </row>
     <row r="22" spans="2:4">
-      <c r="B22" s="14"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="18"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="48"/>
+      <c r="D22" s="49"/>
     </row>
     <row r="23" spans="2:4">
-      <c r="B23" s="14"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="18"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="48"/>
+      <c r="D23" s="49"/>
     </row>
     <row r="24" spans="2:4">
-      <c r="B24" s="14"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="20"/>
+      <c r="B24" s="21"/>
+      <c r="C24" s="50"/>
+      <c r="D24" s="51"/>
     </row>
     <row r="25" spans="2:4">
-      <c r="B25" s="14">
+      <c r="B25" s="21">
         <v>0.27777777777777779</v>
       </c>
-      <c r="C25" s="15"/>
-      <c r="D25" s="16"/>
+      <c r="C25" s="46"/>
+      <c r="D25" s="47"/>
     </row>
     <row r="26" spans="2:4">
-      <c r="B26" s="14"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="18"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="48"/>
+      <c r="D26" s="49"/>
     </row>
     <row r="27" spans="2:4">
-      <c r="B27" s="14"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="18"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="48"/>
+      <c r="D27" s="49"/>
     </row>
     <row r="28" spans="2:4">
-      <c r="B28" s="14"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="18"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="48"/>
+      <c r="D28" s="49"/>
     </row>
     <row r="29" spans="2:4">
-      <c r="B29" s="14"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="18"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="48"/>
+      <c r="D29" s="49"/>
     </row>
     <row r="30" spans="2:4">
-      <c r="B30" s="14"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="18"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="48"/>
+      <c r="D30" s="49"/>
     </row>
     <row r="31" spans="2:4">
-      <c r="B31" s="14"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="18"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="48"/>
+      <c r="D31" s="49"/>
     </row>
     <row r="32" spans="2:4">
-      <c r="B32" s="14"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="18"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="48"/>
+      <c r="D32" s="49"/>
     </row>
     <row r="33" spans="2:4">
-      <c r="B33" s="14"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="18"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="48"/>
+      <c r="D33" s="49"/>
     </row>
     <row r="34" spans="2:4">
-      <c r="B34" s="14"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="20"/>
+      <c r="B34" s="21"/>
+      <c r="C34" s="50"/>
+      <c r="D34" s="51"/>
     </row>
     <row r="35" spans="2:4">
-      <c r="B35" s="14">
+      <c r="B35" s="21">
         <v>0.29166666666666669</v>
       </c>
-      <c r="C35" s="15"/>
-      <c r="D35" s="16"/>
+      <c r="C35" s="46"/>
+      <c r="D35" s="47"/>
     </row>
     <row r="36" spans="2:4">
-      <c r="B36" s="14"/>
-      <c r="C36" s="17"/>
-      <c r="D36" s="18"/>
+      <c r="B36" s="21"/>
+      <c r="C36" s="48"/>
+      <c r="D36" s="49"/>
     </row>
     <row r="37" spans="2:4">
-      <c r="B37" s="14"/>
-      <c r="C37" s="17"/>
-      <c r="D37" s="18"/>
+      <c r="B37" s="21"/>
+      <c r="C37" s="48"/>
+      <c r="D37" s="49"/>
     </row>
     <row r="38" spans="2:4">
-      <c r="B38" s="14"/>
-      <c r="C38" s="17"/>
-      <c r="D38" s="18"/>
+      <c r="B38" s="21"/>
+      <c r="C38" s="48"/>
+      <c r="D38" s="49"/>
     </row>
     <row r="39" spans="2:4">
-      <c r="B39" s="14"/>
-      <c r="C39" s="17"/>
-      <c r="D39" s="18"/>
+      <c r="B39" s="21"/>
+      <c r="C39" s="48"/>
+      <c r="D39" s="49"/>
     </row>
     <row r="40" spans="2:4">
-      <c r="B40" s="14"/>
-      <c r="C40" s="17"/>
-      <c r="D40" s="18"/>
+      <c r="B40" s="21"/>
+      <c r="C40" s="48"/>
+      <c r="D40" s="49"/>
     </row>
     <row r="41" spans="2:4">
-      <c r="B41" s="14"/>
-      <c r="C41" s="17"/>
-      <c r="D41" s="18"/>
+      <c r="B41" s="21"/>
+      <c r="C41" s="48"/>
+      <c r="D41" s="49"/>
     </row>
     <row r="42" spans="2:4">
-      <c r="B42" s="14"/>
-      <c r="C42" s="17"/>
-      <c r="D42" s="18"/>
+      <c r="B42" s="21"/>
+      <c r="C42" s="48"/>
+      <c r="D42" s="49"/>
     </row>
     <row r="43" spans="2:4">
-      <c r="B43" s="14"/>
-      <c r="C43" s="17"/>
-      <c r="D43" s="18"/>
-    </row>
-    <row r="44" spans="2:4" ht="30.75" thickBot="1">
-      <c r="B44" s="21"/>
-      <c r="C44" s="22"/>
-      <c r="D44" s="23"/>
+      <c r="B43" s="21"/>
+      <c r="C43" s="48"/>
+      <c r="D43" s="49"/>
+    </row>
+    <row r="44" spans="2:4" ht="24.75" thickBot="1">
+      <c r="B44" s="33"/>
+      <c r="C44" s="52"/>
+      <c r="D44" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1190,279 +1190,279 @@
       <c r="D2" s="2"/>
     </row>
     <row r="3" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="26" t="s">
+      <c r="B3" s="5"/>
+      <c r="C3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="27"/>
+      <c r="D3" s="7"/>
     </row>
     <row r="4" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A4" s="28"/>
-      <c r="B4" s="29"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="30"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="11"/>
     </row>
     <row r="5" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A5" s="28"/>
-      <c r="B5" s="29"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="30"/>
+      <c r="A5" s="8"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="11"/>
     </row>
     <row r="6" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A6" s="28"/>
-      <c r="B6" s="29"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="30"/>
+      <c r="A6" s="8"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="11"/>
     </row>
     <row r="7" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A7" s="28"/>
-      <c r="B7" s="29"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="30"/>
+      <c r="A7" s="8"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="11"/>
     </row>
     <row r="8" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A8" s="28"/>
-      <c r="B8" s="29"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="30"/>
+      <c r="A8" s="8"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="11"/>
     </row>
     <row r="9" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A9" s="28"/>
-      <c r="B9" s="29"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="30"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="11"/>
     </row>
     <row r="10" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A10" s="28"/>
-      <c r="B10" s="29"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="30"/>
+      <c r="A10" s="8"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="11"/>
     </row>
     <row r="11" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A11" s="28"/>
-      <c r="B11" s="29"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="30"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="11"/>
     </row>
     <row r="12" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A12" s="28"/>
-      <c r="B12" s="29"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="30"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="11"/>
     </row>
     <row r="13" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A13" s="28"/>
-      <c r="B13" s="31"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="32"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="13"/>
     </row>
     <row r="14" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A14" s="28" t="s">
+      <c r="A14" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B14" s="33"/>
-      <c r="C14" s="4" t="s">
+      <c r="B14" s="14"/>
+      <c r="C14" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="D14" s="34"/>
+      <c r="D14" s="15"/>
     </row>
     <row r="15" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A15" s="28"/>
-      <c r="B15" s="29"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="35"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="16"/>
     </row>
     <row r="16" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A16" s="28"/>
-      <c r="B16" s="29"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="35"/>
+      <c r="A16" s="8"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="16"/>
     </row>
     <row r="17" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A17" s="28"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="35"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="16"/>
     </row>
     <row r="18" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A18" s="28"/>
-      <c r="B18" s="29"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="35"/>
+      <c r="A18" s="8"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="16"/>
     </row>
     <row r="19" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A19" s="28"/>
-      <c r="B19" s="29"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="35"/>
+      <c r="A19" s="8"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="16"/>
     </row>
     <row r="20" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A20" s="28"/>
-      <c r="B20" s="29"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="35"/>
+      <c r="A20" s="8"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="16"/>
     </row>
     <row r="21" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A21" s="28"/>
-      <c r="B21" s="29"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="35"/>
+      <c r="A21" s="8"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="16"/>
     </row>
     <row r="22" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A22" s="28"/>
-      <c r="B22" s="29"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="35"/>
+      <c r="A22" s="8"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="16"/>
     </row>
     <row r="23" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A23" s="28"/>
-      <c r="B23" s="29"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="35"/>
+      <c r="A23" s="8"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="16"/>
     </row>
     <row r="24" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A24" s="28"/>
-      <c r="B24" s="31"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="36"/>
+      <c r="A24" s="8"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="17"/>
     </row>
     <row r="25" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A25" s="28" t="s">
+      <c r="A25" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B25" s="37"/>
-      <c r="C25" s="4" t="s">
+      <c r="B25" s="18"/>
+      <c r="C25" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="D25" s="35"/>
+      <c r="D25" s="16"/>
     </row>
     <row r="26" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A26" s="28"/>
-      <c r="B26" s="38"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="35"/>
+      <c r="A26" s="8"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="16"/>
     </row>
     <row r="27" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A27" s="28"/>
-      <c r="B27" s="38"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="35"/>
+      <c r="A27" s="8"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="16"/>
     </row>
     <row r="28" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A28" s="28"/>
-      <c r="B28" s="38"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="35"/>
+      <c r="A28" s="8"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="16"/>
     </row>
     <row r="29" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A29" s="28"/>
-      <c r="B29" s="38"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="35"/>
+      <c r="A29" s="8"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="16"/>
     </row>
     <row r="30" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A30" s="28"/>
-      <c r="B30" s="38"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="35"/>
+      <c r="A30" s="8"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="16"/>
     </row>
     <row r="31" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A31" s="28"/>
-      <c r="B31" s="38"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="35"/>
+      <c r="A31" s="8"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="16"/>
     </row>
     <row r="32" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A32" s="28"/>
-      <c r="B32" s="38"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="35"/>
+      <c r="A32" s="8"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="16"/>
     </row>
     <row r="33" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A33" s="28"/>
-      <c r="B33" s="38"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="35"/>
+      <c r="A33" s="8"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="16"/>
     </row>
     <row r="34" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A34" s="28"/>
-      <c r="B34" s="38"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="35"/>
+      <c r="A34" s="8"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="16"/>
     </row>
     <row r="35" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A35" s="28"/>
-      <c r="B35" s="39"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="35"/>
+      <c r="A35" s="8"/>
+      <c r="B35" s="20"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="16"/>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="14"/>
-      <c r="B36" s="40" t="s">
+      <c r="A36" s="21"/>
+      <c r="B36" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="C36" s="41" t="s">
+      <c r="C36" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D36" s="42"/>
+      <c r="D36" s="24"/>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="14"/>
-      <c r="B37" s="43"/>
-      <c r="C37" s="44"/>
-      <c r="D37" s="45"/>
+      <c r="A37" s="21"/>
+      <c r="B37" s="25"/>
+      <c r="C37" s="26"/>
+      <c r="D37" s="27"/>
     </row>
     <row r="38" spans="1:4" ht="24" customHeight="1">
-      <c r="A38" s="14"/>
-      <c r="B38" s="46" t="s">
+      <c r="A38" s="21"/>
+      <c r="B38" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="C38" s="47" t="s">
+      <c r="C38" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="D38" s="48"/>
+      <c r="D38" s="30"/>
     </row>
     <row r="39" spans="1:4" ht="24" customHeight="1">
-      <c r="A39" s="14"/>
-      <c r="B39" s="46" t="s">
+      <c r="A39" s="21"/>
+      <c r="B39" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C39" s="49"/>
-      <c r="D39" s="50"/>
+      <c r="C39" s="31"/>
+      <c r="D39" s="32"/>
     </row>
     <row r="40" spans="1:4" ht="24" customHeight="1">
-      <c r="A40" s="14"/>
-      <c r="B40" s="29"/>
-      <c r="C40" s="49" t="s">
+      <c r="A40" s="21"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="D40" s="50"/>
-    </row>
-    <row r="41" spans="1:4" ht="30.75" thickBot="1">
-      <c r="A41" s="21"/>
-      <c r="B41" s="51"/>
-      <c r="C41" s="52"/>
-      <c r="D41" s="53"/>
+      <c r="D40" s="32"/>
+    </row>
+    <row r="41" spans="1:4" ht="24.75" thickBot="1">
+      <c r="A41" s="33"/>
+      <c r="B41" s="34"/>
+      <c r="C41" s="35"/>
+      <c r="D41" s="36"/>
     </row>
     <row r="43" spans="1:4">
       <c r="D43" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A36:A41"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:D37"/>
-    <mergeCell ref="C38:D39"/>
-    <mergeCell ref="C40:D41"/>
     <mergeCell ref="A3:A13"/>
     <mergeCell ref="C3:C13"/>
     <mergeCell ref="A14:A24"/>
     <mergeCell ref="C14:C24"/>
     <mergeCell ref="A25:A35"/>
     <mergeCell ref="C25:C35"/>
+    <mergeCell ref="A36:A41"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:D37"/>
+    <mergeCell ref="C38:D39"/>
+    <mergeCell ref="C40:D41"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.70866141732283472" right="0.31496062992125984" top="0.74803149606299213" bottom="0.55118110236220474" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/bus_booking1.xlsx
+++ b/bus_booking1.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\front2\OneDrive\ドキュメント\bus-booking\Xe bus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56552EC4-8DA1-424B-B179-DA33EC2A2C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA18AC3A-AE3D-429F-A686-57B03B16E80A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{42734889-29B0-4E0D-9607-DDF20B1FC993}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{42734889-29B0-4E0D-9607-DDF20B1FC993}"/>
   </bookViews>
   <sheets>
     <sheet name="6-7" sheetId="2" r:id="rId1"/>
     <sheet name="7-10" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'6-7'!$A$1:$D$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'7-10'!$A$1:$D$41</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -538,21 +539,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
@@ -563,52 +552,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="20" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="20" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
@@ -638,6 +585,60 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -921,241 +922,242 @@
   <dimension ref="B1:D44"/>
   <sheetFormatPr defaultRowHeight="24"/>
   <cols>
-    <col min="1" max="1" width="3.25" style="37" customWidth="1"/>
-    <col min="2" max="2" width="9" style="37"/>
-    <col min="3" max="4" width="42.625" style="37" customWidth="1"/>
-    <col min="5" max="16384" width="9" style="37"/>
+    <col min="1" max="1" width="3.25" style="19" customWidth="1"/>
+    <col min="2" max="2" width="9" style="19"/>
+    <col min="3" max="3" width="54" style="19" customWidth="1"/>
+    <col min="4" max="4" width="55.125" style="19" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="19"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:4">
-      <c r="D1" s="38" t="s">
+      <c r="D1" s="20" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="2:4" ht="9.75" customHeight="1" thickBot="1">
-      <c r="D2" s="39"/>
+      <c r="D2" s="21"/>
     </row>
     <row r="3" spans="2:4" ht="24.95" customHeight="1">
-      <c r="B3" s="40"/>
-      <c r="C3" s="41" t="s">
+      <c r="B3" s="22"/>
+      <c r="C3" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="42" t="s">
+      <c r="D3" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" spans="2:4" ht="10.5" customHeight="1">
-      <c r="B4" s="43"/>
-      <c r="C4" s="44"/>
-      <c r="D4" s="45"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="27"/>
     </row>
     <row r="5" spans="2:4">
-      <c r="B5" s="21">
+      <c r="B5" s="36">
         <v>0.25347222222222221</v>
       </c>
-      <c r="C5" s="46"/>
-      <c r="D5" s="47"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="29"/>
     </row>
     <row r="6" spans="2:4">
-      <c r="B6" s="21"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="49"/>
+      <c r="B6" s="36"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="31"/>
     </row>
     <row r="7" spans="2:4">
-      <c r="B7" s="21"/>
-      <c r="C7" s="48"/>
-      <c r="D7" s="49"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="31"/>
     </row>
     <row r="8" spans="2:4">
-      <c r="B8" s="21"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="49"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="31"/>
     </row>
     <row r="9" spans="2:4">
-      <c r="B9" s="21"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="49"/>
+      <c r="B9" s="36"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="31"/>
     </row>
     <row r="10" spans="2:4">
-      <c r="B10" s="21"/>
-      <c r="C10" s="48"/>
-      <c r="D10" s="49"/>
+      <c r="B10" s="36"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="31"/>
     </row>
     <row r="11" spans="2:4">
-      <c r="B11" s="21"/>
-      <c r="C11" s="48"/>
-      <c r="D11" s="49"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="31"/>
     </row>
     <row r="12" spans="2:4">
-      <c r="B12" s="21"/>
-      <c r="C12" s="48"/>
-      <c r="D12" s="49"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="31"/>
     </row>
     <row r="13" spans="2:4">
-      <c r="B13" s="21"/>
-      <c r="C13" s="48"/>
-      <c r="D13" s="49"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="31"/>
     </row>
     <row r="14" spans="2:4">
-      <c r="B14" s="21"/>
-      <c r="C14" s="50"/>
-      <c r="D14" s="51"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="33"/>
     </row>
     <row r="15" spans="2:4">
-      <c r="B15" s="21">
+      <c r="B15" s="36">
         <v>0.2638888888888889</v>
       </c>
-      <c r="C15" s="46"/>
-      <c r="D15" s="47"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="29"/>
     </row>
     <row r="16" spans="2:4">
-      <c r="B16" s="21"/>
-      <c r="C16" s="48"/>
-      <c r="D16" s="49"/>
+      <c r="B16" s="36"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="31"/>
     </row>
     <row r="17" spans="2:4">
-      <c r="B17" s="21"/>
-      <c r="C17" s="48"/>
-      <c r="D17" s="49"/>
+      <c r="B17" s="36"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="31"/>
     </row>
     <row r="18" spans="2:4">
-      <c r="B18" s="21"/>
-      <c r="C18" s="48"/>
-      <c r="D18" s="49"/>
+      <c r="B18" s="36"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="31"/>
     </row>
     <row r="19" spans="2:4">
-      <c r="B19" s="21"/>
-      <c r="C19" s="48"/>
-      <c r="D19" s="49"/>
+      <c r="B19" s="36"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="31"/>
     </row>
     <row r="20" spans="2:4">
-      <c r="B20" s="21"/>
-      <c r="C20" s="48"/>
-      <c r="D20" s="49"/>
+      <c r="B20" s="36"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="31"/>
     </row>
     <row r="21" spans="2:4">
-      <c r="B21" s="21"/>
-      <c r="C21" s="48"/>
-      <c r="D21" s="49"/>
+      <c r="B21" s="36"/>
+      <c r="C21" s="30"/>
+      <c r="D21" s="31"/>
     </row>
     <row r="22" spans="2:4">
-      <c r="B22" s="21"/>
-      <c r="C22" s="48"/>
-      <c r="D22" s="49"/>
+      <c r="B22" s="36"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="31"/>
     </row>
     <row r="23" spans="2:4">
-      <c r="B23" s="21"/>
-      <c r="C23" s="48"/>
-      <c r="D23" s="49"/>
+      <c r="B23" s="36"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="31"/>
     </row>
     <row r="24" spans="2:4">
-      <c r="B24" s="21"/>
-      <c r="C24" s="50"/>
-      <c r="D24" s="51"/>
+      <c r="B24" s="36"/>
+      <c r="C24" s="32"/>
+      <c r="D24" s="33"/>
     </row>
     <row r="25" spans="2:4">
-      <c r="B25" s="21">
+      <c r="B25" s="36">
         <v>0.27777777777777779</v>
       </c>
-      <c r="C25" s="46"/>
-      <c r="D25" s="47"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="29"/>
     </row>
     <row r="26" spans="2:4">
-      <c r="B26" s="21"/>
-      <c r="C26" s="48"/>
-      <c r="D26" s="49"/>
+      <c r="B26" s="36"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="31"/>
     </row>
     <row r="27" spans="2:4">
-      <c r="B27" s="21"/>
-      <c r="C27" s="48"/>
-      <c r="D27" s="49"/>
+      <c r="B27" s="36"/>
+      <c r="C27" s="30"/>
+      <c r="D27" s="31"/>
     </row>
     <row r="28" spans="2:4">
-      <c r="B28" s="21"/>
-      <c r="C28" s="48"/>
-      <c r="D28" s="49"/>
+      <c r="B28" s="36"/>
+      <c r="C28" s="30"/>
+      <c r="D28" s="31"/>
     </row>
     <row r="29" spans="2:4">
-      <c r="B29" s="21"/>
-      <c r="C29" s="48"/>
-      <c r="D29" s="49"/>
+      <c r="B29" s="36"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="31"/>
     </row>
     <row r="30" spans="2:4">
-      <c r="B30" s="21"/>
-      <c r="C30" s="48"/>
-      <c r="D30" s="49"/>
+      <c r="B30" s="36"/>
+      <c r="C30" s="30"/>
+      <c r="D30" s="31"/>
     </row>
     <row r="31" spans="2:4">
-      <c r="B31" s="21"/>
-      <c r="C31" s="48"/>
-      <c r="D31" s="49"/>
+      <c r="B31" s="36"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="31"/>
     </row>
     <row r="32" spans="2:4">
-      <c r="B32" s="21"/>
-      <c r="C32" s="48"/>
-      <c r="D32" s="49"/>
+      <c r="B32" s="36"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="31"/>
     </row>
     <row r="33" spans="2:4">
-      <c r="B33" s="21"/>
-      <c r="C33" s="48"/>
-      <c r="D33" s="49"/>
+      <c r="B33" s="36"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="31"/>
     </row>
     <row r="34" spans="2:4">
-      <c r="B34" s="21"/>
-      <c r="C34" s="50"/>
-      <c r="D34" s="51"/>
+      <c r="B34" s="36"/>
+      <c r="C34" s="32"/>
+      <c r="D34" s="33"/>
     </row>
     <row r="35" spans="2:4">
-      <c r="B35" s="21">
+      <c r="B35" s="36">
         <v>0.29166666666666669</v>
       </c>
-      <c r="C35" s="46"/>
-      <c r="D35" s="47"/>
+      <c r="C35" s="28"/>
+      <c r="D35" s="29"/>
     </row>
     <row r="36" spans="2:4">
-      <c r="B36" s="21"/>
-      <c r="C36" s="48"/>
-      <c r="D36" s="49"/>
+      <c r="B36" s="36"/>
+      <c r="C36" s="30"/>
+      <c r="D36" s="31"/>
     </row>
     <row r="37" spans="2:4">
-      <c r="B37" s="21"/>
-      <c r="C37" s="48"/>
-      <c r="D37" s="49"/>
+      <c r="B37" s="36"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="31"/>
     </row>
     <row r="38" spans="2:4">
-      <c r="B38" s="21"/>
-      <c r="C38" s="48"/>
-      <c r="D38" s="49"/>
+      <c r="B38" s="36"/>
+      <c r="C38" s="30"/>
+      <c r="D38" s="31"/>
     </row>
     <row r="39" spans="2:4">
-      <c r="B39" s="21"/>
-      <c r="C39" s="48"/>
-      <c r="D39" s="49"/>
+      <c r="B39" s="36"/>
+      <c r="C39" s="30"/>
+      <c r="D39" s="31"/>
     </row>
     <row r="40" spans="2:4">
-      <c r="B40" s="21"/>
-      <c r="C40" s="48"/>
-      <c r="D40" s="49"/>
+      <c r="B40" s="36"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="31"/>
     </row>
     <row r="41" spans="2:4">
-      <c r="B41" s="21"/>
-      <c r="C41" s="48"/>
-      <c r="D41" s="49"/>
+      <c r="B41" s="36"/>
+      <c r="C41" s="30"/>
+      <c r="D41" s="31"/>
     </row>
     <row r="42" spans="2:4">
-      <c r="B42" s="21"/>
-      <c r="C42" s="48"/>
-      <c r="D42" s="49"/>
+      <c r="B42" s="36"/>
+      <c r="C42" s="30"/>
+      <c r="D42" s="31"/>
     </row>
     <row r="43" spans="2:4">
-      <c r="B43" s="21"/>
-      <c r="C43" s="48"/>
-      <c r="D43" s="49"/>
+      <c r="B43" s="36"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="31"/>
     </row>
     <row r="44" spans="2:4" ht="24.75" thickBot="1">
-      <c r="B44" s="33"/>
-      <c r="C44" s="52"/>
-      <c r="D44" s="53"/>
+      <c r="B44" s="37"/>
+      <c r="C44" s="34"/>
+      <c r="D44" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1165,8 +1167,8 @@
     <mergeCell ref="B35:B44"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="90" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.23622047244094491" right="0" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="72" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1190,279 +1192,279 @@
       <c r="D2" s="2"/>
     </row>
     <row r="3" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="6" t="s">
+      <c r="B3" s="4"/>
+      <c r="C3" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="7"/>
+      <c r="D3" s="5"/>
     </row>
     <row r="4" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A4" s="8"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="11"/>
+      <c r="A4" s="39"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="7"/>
     </row>
     <row r="5" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A5" s="8"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="11"/>
+      <c r="A5" s="39"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="7"/>
     </row>
     <row r="6" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A6" s="8"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="11"/>
+      <c r="A6" s="39"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="7"/>
     </row>
     <row r="7" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A7" s="8"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="11"/>
+      <c r="A7" s="39"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="7"/>
     </row>
     <row r="8" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A8" s="8"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="11"/>
+      <c r="A8" s="39"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="7"/>
     </row>
     <row r="9" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A9" s="8"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="11"/>
+      <c r="A9" s="39"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="7"/>
     </row>
     <row r="10" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A10" s="8"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="11"/>
+      <c r="A10" s="39"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="7"/>
     </row>
     <row r="11" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A11" s="8"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="11"/>
+      <c r="A11" s="39"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="7"/>
     </row>
     <row r="12" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A12" s="8"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="11"/>
+      <c r="A12" s="39"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="7"/>
     </row>
     <row r="13" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A13" s="8"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="13"/>
+      <c r="A13" s="39"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="9"/>
     </row>
     <row r="14" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="B14" s="14"/>
-      <c r="C14" s="10" t="s">
+      <c r="B14" s="10"/>
+      <c r="C14" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="D14" s="15"/>
+      <c r="D14" s="11"/>
     </row>
     <row r="15" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A15" s="8"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="16"/>
+      <c r="A15" s="39"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="12"/>
     </row>
     <row r="16" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A16" s="8"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="16"/>
+      <c r="A16" s="39"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="12"/>
     </row>
     <row r="17" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A17" s="8"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="16"/>
+      <c r="A17" s="39"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="12"/>
     </row>
     <row r="18" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A18" s="8"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="16"/>
+      <c r="A18" s="39"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="12"/>
     </row>
     <row r="19" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A19" s="8"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="16"/>
+      <c r="A19" s="39"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="12"/>
     </row>
     <row r="20" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A20" s="8"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="16"/>
+      <c r="A20" s="39"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="12"/>
     </row>
     <row r="21" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A21" s="8"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="16"/>
+      <c r="A21" s="39"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="12"/>
     </row>
     <row r="22" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A22" s="8"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="16"/>
+      <c r="A22" s="39"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="41"/>
+      <c r="D22" s="12"/>
     </row>
     <row r="23" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A23" s="8"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="16"/>
+      <c r="A23" s="39"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="41"/>
+      <c r="D23" s="12"/>
     </row>
     <row r="24" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A24" s="8"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="17"/>
+      <c r="A24" s="39"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="13"/>
     </row>
     <row r="25" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="B25" s="18"/>
-      <c r="C25" s="10" t="s">
+      <c r="B25" s="14"/>
+      <c r="C25" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="D25" s="16"/>
+      <c r="D25" s="12"/>
     </row>
     <row r="26" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A26" s="8"/>
-      <c r="B26" s="19"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="16"/>
+      <c r="A26" s="39"/>
+      <c r="B26" s="15"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="12"/>
     </row>
     <row r="27" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A27" s="8"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="16"/>
+      <c r="A27" s="39"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="12"/>
     </row>
     <row r="28" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A28" s="8"/>
-      <c r="B28" s="19"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="16"/>
+      <c r="A28" s="39"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="41"/>
+      <c r="D28" s="12"/>
     </row>
     <row r="29" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A29" s="8"/>
-      <c r="B29" s="19"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="16"/>
+      <c r="A29" s="39"/>
+      <c r="B29" s="15"/>
+      <c r="C29" s="41"/>
+      <c r="D29" s="12"/>
     </row>
     <row r="30" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A30" s="8"/>
-      <c r="B30" s="19"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="16"/>
+      <c r="A30" s="39"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="41"/>
+      <c r="D30" s="12"/>
     </row>
     <row r="31" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A31" s="8"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="16"/>
+      <c r="A31" s="39"/>
+      <c r="B31" s="15"/>
+      <c r="C31" s="41"/>
+      <c r="D31" s="12"/>
     </row>
     <row r="32" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A32" s="8"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="16"/>
+      <c r="A32" s="39"/>
+      <c r="B32" s="15"/>
+      <c r="C32" s="41"/>
+      <c r="D32" s="12"/>
     </row>
     <row r="33" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A33" s="8"/>
-      <c r="B33" s="19"/>
-      <c r="C33" s="10"/>
-      <c r="D33" s="16"/>
+      <c r="A33" s="39"/>
+      <c r="B33" s="15"/>
+      <c r="C33" s="41"/>
+      <c r="D33" s="12"/>
     </row>
     <row r="34" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A34" s="8"/>
-      <c r="B34" s="19"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="16"/>
+      <c r="A34" s="39"/>
+      <c r="B34" s="15"/>
+      <c r="C34" s="41"/>
+      <c r="D34" s="12"/>
     </row>
     <row r="35" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A35" s="8"/>
-      <c r="B35" s="20"/>
-      <c r="C35" s="10"/>
-      <c r="D35" s="16"/>
+      <c r="A35" s="39"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="41"/>
+      <c r="D35" s="12"/>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="21"/>
-      <c r="B36" s="22" t="s">
+      <c r="A36" s="36"/>
+      <c r="B36" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="C36" s="23" t="s">
+      <c r="C36" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="D36" s="24"/>
+      <c r="D36" s="45"/>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="21"/>
-      <c r="B37" s="25"/>
-      <c r="C37" s="26"/>
-      <c r="D37" s="27"/>
+      <c r="A37" s="36"/>
+      <c r="B37" s="43"/>
+      <c r="C37" s="46"/>
+      <c r="D37" s="47"/>
     </row>
     <row r="38" spans="1:4" ht="24" customHeight="1">
-      <c r="A38" s="21"/>
-      <c r="B38" s="28" t="s">
+      <c r="A38" s="36"/>
+      <c r="B38" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C38" s="29" t="s">
+      <c r="C38" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="D38" s="30"/>
+      <c r="D38" s="49"/>
     </row>
     <row r="39" spans="1:4" ht="24" customHeight="1">
-      <c r="A39" s="21"/>
-      <c r="B39" s="28" t="s">
+      <c r="A39" s="36"/>
+      <c r="B39" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C39" s="31"/>
-      <c r="D39" s="32"/>
+      <c r="C39" s="50"/>
+      <c r="D39" s="51"/>
     </row>
     <row r="40" spans="1:4" ht="24" customHeight="1">
-      <c r="A40" s="21"/>
-      <c r="B40" s="9"/>
-      <c r="C40" s="31" t="s">
+      <c r="A40" s="36"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="D40" s="32"/>
+      <c r="D40" s="51"/>
     </row>
     <row r="41" spans="1:4" ht="24.75" thickBot="1">
-      <c r="A41" s="33"/>
-      <c r="B41" s="34"/>
-      <c r="C41" s="35"/>
-      <c r="D41" s="36"/>
+      <c r="A41" s="37"/>
+      <c r="B41" s="18"/>
+      <c r="C41" s="52"/>
+      <c r="D41" s="53"/>
     </row>
     <row r="43" spans="1:4">
       <c r="D43" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A36:A41"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:D37"/>
+    <mergeCell ref="C38:D39"/>
+    <mergeCell ref="C40:D41"/>
     <mergeCell ref="A3:A13"/>
     <mergeCell ref="C3:C13"/>
     <mergeCell ref="A14:A24"/>
     <mergeCell ref="C14:C24"/>
     <mergeCell ref="A25:A35"/>
     <mergeCell ref="C25:C35"/>
-    <mergeCell ref="A36:A41"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:D37"/>
-    <mergeCell ref="C38:D39"/>
-    <mergeCell ref="C40:D41"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.70866141732283472" right="0.31496062992125984" top="0.74803149606299213" bottom="0.55118110236220474" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/bus_booking1.xlsx
+++ b/bus_booking1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\front2\OneDrive\ドキュメント\bus-booking\Xe bus\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a72beccc240b2c87/デスクトップ/ファム/bus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA18AC3A-AE3D-429F-A686-57B03B16E80A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{CA18AC3A-AE3D-429F-A686-57B03B16E80A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B933030-71AC-4FF4-AC2B-9833CE24779C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{42734889-29B0-4E0D-9607-DDF20B1FC993}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{42734889-29B0-4E0D-9607-DDF20B1FC993}"/>
   </bookViews>
   <sheets>
     <sheet name="6-7" sheetId="2" r:id="rId1"/>
@@ -165,7 +165,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="14"/>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Yu Gothic"/>
       <family val="3"/>
@@ -528,16 +529,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
@@ -556,89 +551,87 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="20" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -922,242 +915,242 @@
   <dimension ref="B1:D44"/>
   <sheetFormatPr defaultRowHeight="24"/>
   <cols>
-    <col min="1" max="1" width="3.25" style="19" customWidth="1"/>
-    <col min="2" max="2" width="9" style="19"/>
-    <col min="3" max="3" width="54" style="19" customWidth="1"/>
-    <col min="4" max="4" width="55.125" style="19" customWidth="1"/>
-    <col min="5" max="16384" width="9" style="19"/>
+    <col min="1" max="1" width="3.25" style="41" customWidth="1"/>
+    <col min="2" max="2" width="9" style="41"/>
+    <col min="3" max="3" width="54" style="41" customWidth="1"/>
+    <col min="4" max="4" width="55.125" style="41" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="41"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4">
-      <c r="D1" s="20" t="s">
+    <row r="1" spans="2:4" s="41" customFormat="1">
+      <c r="D1" s="17" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="2:4" ht="9.75" customHeight="1" thickBot="1">
-      <c r="D2" s="21"/>
-    </row>
-    <row r="3" spans="2:4" ht="24.95" customHeight="1">
-      <c r="B3" s="22"/>
-      <c r="C3" s="23" t="s">
+    <row r="2" spans="2:4" s="41" customFormat="1" ht="9.75" customHeight="1" thickBot="1">
+      <c r="D2" s="17"/>
+    </row>
+    <row r="3" spans="2:4" s="41" customFormat="1" ht="24.95" customHeight="1">
+      <c r="B3" s="42"/>
+      <c r="C3" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="24" t="s">
+      <c r="D3" s="19" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="10.5" customHeight="1">
-      <c r="B4" s="25"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="27"/>
-    </row>
-    <row r="5" spans="2:4">
-      <c r="B5" s="36">
+    <row r="4" spans="2:4" s="41" customFormat="1" ht="10.5" customHeight="1">
+      <c r="B4" s="43"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="45"/>
+    </row>
+    <row r="5" spans="2:4" s="41" customFormat="1">
+      <c r="B5" s="20">
         <v>0.25347222222222221</v>
       </c>
-      <c r="C5" s="28"/>
-      <c r="D5" s="29"/>
-    </row>
-    <row r="6" spans="2:4">
-      <c r="B6" s="36"/>
-      <c r="C6" s="30"/>
-      <c r="D6" s="31"/>
-    </row>
-    <row r="7" spans="2:4">
-      <c r="B7" s="36"/>
-      <c r="C7" s="30"/>
-      <c r="D7" s="31"/>
-    </row>
-    <row r="8" spans="2:4">
-      <c r="B8" s="36"/>
-      <c r="C8" s="30"/>
-      <c r="D8" s="31"/>
-    </row>
-    <row r="9" spans="2:4">
-      <c r="B9" s="36"/>
-      <c r="C9" s="30"/>
-      <c r="D9" s="31"/>
-    </row>
-    <row r="10" spans="2:4">
-      <c r="B10" s="36"/>
-      <c r="C10" s="30"/>
-      <c r="D10" s="31"/>
-    </row>
-    <row r="11" spans="2:4">
-      <c r="B11" s="36"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="31"/>
-    </row>
-    <row r="12" spans="2:4">
-      <c r="B12" s="36"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="31"/>
-    </row>
-    <row r="13" spans="2:4">
-      <c r="B13" s="36"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="31"/>
-    </row>
-    <row r="14" spans="2:4">
-      <c r="B14" s="36"/>
-      <c r="C14" s="32"/>
-      <c r="D14" s="33"/>
-    </row>
-    <row r="15" spans="2:4">
-      <c r="B15" s="36">
+      <c r="C5" s="12"/>
+      <c r="D5" s="9"/>
+    </row>
+    <row r="6" spans="2:4" s="41" customFormat="1">
+      <c r="B6" s="20"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="10"/>
+    </row>
+    <row r="7" spans="2:4" s="41" customFormat="1">
+      <c r="B7" s="20"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="10"/>
+    </row>
+    <row r="8" spans="2:4" s="41" customFormat="1">
+      <c r="B8" s="20"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="10"/>
+    </row>
+    <row r="9" spans="2:4" s="41" customFormat="1">
+      <c r="B9" s="20"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="10"/>
+    </row>
+    <row r="10" spans="2:4" s="41" customFormat="1">
+      <c r="B10" s="20"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="10"/>
+    </row>
+    <row r="11" spans="2:4" s="41" customFormat="1">
+      <c r="B11" s="20"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="10"/>
+    </row>
+    <row r="12" spans="2:4" s="41" customFormat="1">
+      <c r="B12" s="20"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="10"/>
+    </row>
+    <row r="13" spans="2:4" s="41" customFormat="1">
+      <c r="B13" s="20"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="10"/>
+    </row>
+    <row r="14" spans="2:4" s="41" customFormat="1">
+      <c r="B14" s="20"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="11"/>
+    </row>
+    <row r="15" spans="2:4" s="41" customFormat="1">
+      <c r="B15" s="20">
         <v>0.2638888888888889</v>
       </c>
-      <c r="C15" s="28"/>
-      <c r="D15" s="29"/>
-    </row>
-    <row r="16" spans="2:4">
-      <c r="B16" s="36"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="31"/>
-    </row>
-    <row r="17" spans="2:4">
-      <c r="B17" s="36"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="31"/>
-    </row>
-    <row r="18" spans="2:4">
-      <c r="B18" s="36"/>
-      <c r="C18" s="30"/>
-      <c r="D18" s="31"/>
-    </row>
-    <row r="19" spans="2:4">
-      <c r="B19" s="36"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="31"/>
-    </row>
-    <row r="20" spans="2:4">
-      <c r="B20" s="36"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="31"/>
-    </row>
-    <row r="21" spans="2:4">
-      <c r="B21" s="36"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="31"/>
-    </row>
-    <row r="22" spans="2:4">
-      <c r="B22" s="36"/>
-      <c r="C22" s="30"/>
-      <c r="D22" s="31"/>
-    </row>
-    <row r="23" spans="2:4">
-      <c r="B23" s="36"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="31"/>
-    </row>
-    <row r="24" spans="2:4">
-      <c r="B24" s="36"/>
-      <c r="C24" s="32"/>
-      <c r="D24" s="33"/>
-    </row>
-    <row r="25" spans="2:4">
-      <c r="B25" s="36">
+      <c r="C15" s="12"/>
+      <c r="D15" s="9"/>
+    </row>
+    <row r="16" spans="2:4" s="41" customFormat="1">
+      <c r="B16" s="20"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="10"/>
+    </row>
+    <row r="17" spans="2:4" s="41" customFormat="1">
+      <c r="B17" s="20"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="10"/>
+    </row>
+    <row r="18" spans="2:4" s="41" customFormat="1">
+      <c r="B18" s="20"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="10"/>
+    </row>
+    <row r="19" spans="2:4" s="41" customFormat="1">
+      <c r="B19" s="20"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="10"/>
+    </row>
+    <row r="20" spans="2:4" s="41" customFormat="1">
+      <c r="B20" s="20"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="10"/>
+    </row>
+    <row r="21" spans="2:4" s="41" customFormat="1">
+      <c r="B21" s="20"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="10"/>
+    </row>
+    <row r="22" spans="2:4" s="41" customFormat="1">
+      <c r="B22" s="20"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="10"/>
+    </row>
+    <row r="23" spans="2:4" s="41" customFormat="1">
+      <c r="B23" s="20"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="10"/>
+    </row>
+    <row r="24" spans="2:4" s="41" customFormat="1">
+      <c r="B24" s="20"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="11"/>
+    </row>
+    <row r="25" spans="2:4" s="41" customFormat="1">
+      <c r="B25" s="20">
         <v>0.27777777777777779</v>
       </c>
-      <c r="C25" s="28"/>
-      <c r="D25" s="29"/>
-    </row>
-    <row r="26" spans="2:4">
-      <c r="B26" s="36"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="31"/>
-    </row>
-    <row r="27" spans="2:4">
-      <c r="B27" s="36"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="31"/>
-    </row>
-    <row r="28" spans="2:4">
-      <c r="B28" s="36"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="31"/>
-    </row>
-    <row r="29" spans="2:4">
-      <c r="B29" s="36"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="31"/>
-    </row>
-    <row r="30" spans="2:4">
-      <c r="B30" s="36"/>
-      <c r="C30" s="30"/>
-      <c r="D30" s="31"/>
-    </row>
-    <row r="31" spans="2:4">
-      <c r="B31" s="36"/>
-      <c r="C31" s="30"/>
-      <c r="D31" s="31"/>
-    </row>
-    <row r="32" spans="2:4">
-      <c r="B32" s="36"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="31"/>
-    </row>
-    <row r="33" spans="2:4">
-      <c r="B33" s="36"/>
-      <c r="C33" s="30"/>
-      <c r="D33" s="31"/>
-    </row>
-    <row r="34" spans="2:4">
-      <c r="B34" s="36"/>
-      <c r="C34" s="32"/>
-      <c r="D34" s="33"/>
-    </row>
-    <row r="35" spans="2:4">
-      <c r="B35" s="36">
+      <c r="C25" s="12"/>
+      <c r="D25" s="9"/>
+    </row>
+    <row r="26" spans="2:4" s="41" customFormat="1">
+      <c r="B26" s="20"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="10"/>
+    </row>
+    <row r="27" spans="2:4" s="41" customFormat="1">
+      <c r="B27" s="20"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="10"/>
+    </row>
+    <row r="28" spans="2:4" s="41" customFormat="1">
+      <c r="B28" s="20"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="10"/>
+    </row>
+    <row r="29" spans="2:4" s="41" customFormat="1">
+      <c r="B29" s="20"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="10"/>
+    </row>
+    <row r="30" spans="2:4" s="41" customFormat="1">
+      <c r="B30" s="20"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="10"/>
+    </row>
+    <row r="31" spans="2:4" s="41" customFormat="1">
+      <c r="B31" s="20"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="10"/>
+    </row>
+    <row r="32" spans="2:4" s="41" customFormat="1">
+      <c r="B32" s="20"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="10"/>
+    </row>
+    <row r="33" spans="2:4" s="41" customFormat="1">
+      <c r="B33" s="20"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="10"/>
+    </row>
+    <row r="34" spans="2:4" s="41" customFormat="1">
+      <c r="B34" s="20"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="11"/>
+    </row>
+    <row r="35" spans="2:4" s="41" customFormat="1">
+      <c r="B35" s="20">
         <v>0.29166666666666669</v>
       </c>
-      <c r="C35" s="28"/>
-      <c r="D35" s="29"/>
-    </row>
-    <row r="36" spans="2:4">
-      <c r="B36" s="36"/>
-      <c r="C36" s="30"/>
-      <c r="D36" s="31"/>
-    </row>
-    <row r="37" spans="2:4">
-      <c r="B37" s="36"/>
-      <c r="C37" s="30"/>
-      <c r="D37" s="31"/>
-    </row>
-    <row r="38" spans="2:4">
-      <c r="B38" s="36"/>
-      <c r="C38" s="30"/>
-      <c r="D38" s="31"/>
-    </row>
-    <row r="39" spans="2:4">
-      <c r="B39" s="36"/>
-      <c r="C39" s="30"/>
-      <c r="D39" s="31"/>
-    </row>
-    <row r="40" spans="2:4">
-      <c r="B40" s="36"/>
-      <c r="C40" s="30"/>
-      <c r="D40" s="31"/>
-    </row>
-    <row r="41" spans="2:4">
-      <c r="B41" s="36"/>
-      <c r="C41" s="30"/>
-      <c r="D41" s="31"/>
-    </row>
-    <row r="42" spans="2:4">
-      <c r="B42" s="36"/>
-      <c r="C42" s="30"/>
-      <c r="D42" s="31"/>
-    </row>
-    <row r="43" spans="2:4">
-      <c r="B43" s="36"/>
-      <c r="C43" s="30"/>
-      <c r="D43" s="31"/>
-    </row>
-    <row r="44" spans="2:4" ht="24.75" thickBot="1">
-      <c r="B44" s="37"/>
-      <c r="C44" s="34"/>
-      <c r="D44" s="35"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="9"/>
+    </row>
+    <row r="36" spans="2:4" s="41" customFormat="1">
+      <c r="B36" s="20"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="10"/>
+    </row>
+    <row r="37" spans="2:4" s="41" customFormat="1">
+      <c r="B37" s="20"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="10"/>
+    </row>
+    <row r="38" spans="2:4" s="41" customFormat="1">
+      <c r="B38" s="20"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="10"/>
+    </row>
+    <row r="39" spans="2:4" s="41" customFormat="1">
+      <c r="B39" s="20"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="10"/>
+    </row>
+    <row r="40" spans="2:4" s="41" customFormat="1">
+      <c r="B40" s="20"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="10"/>
+    </row>
+    <row r="41" spans="2:4" s="41" customFormat="1">
+      <c r="B41" s="20"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="10"/>
+    </row>
+    <row r="42" spans="2:4" s="41" customFormat="1">
+      <c r="B42" s="20"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="10"/>
+    </row>
+    <row r="43" spans="2:4" s="41" customFormat="1">
+      <c r="B43" s="20"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="10"/>
+    </row>
+    <row r="44" spans="2:4" s="41" customFormat="1" ht="24.75" thickBot="1">
+      <c r="B44" s="21"/>
+      <c r="C44" s="46"/>
+      <c r="D44" s="47"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1175,12 +1168,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8BB9E68-6C31-49D2-98C6-9B33C5FA8717}">
   <dimension ref="A1:D43"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="7.625" customWidth="1"/>
-    <col min="2" max="2" width="53.625" customWidth="1"/>
-    <col min="3" max="3" width="7.625" customWidth="1"/>
-    <col min="4" max="4" width="53.625" customWidth="1"/>
+    <col min="1" max="1" width="7.625" style="38" customWidth="1"/>
+    <col min="2" max="2" width="53.625" style="38" customWidth="1"/>
+    <col min="3" max="3" width="7.625" style="38" customWidth="1"/>
+    <col min="4" max="4" width="53.625" style="38" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="38"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="25.5">
@@ -1189,282 +1183,282 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="9.75" customHeight="1" thickBot="1">
-      <c r="D2" s="2"/>
+      <c r="D2" s="39"/>
     </row>
     <row r="3" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="40" t="s">
+      <c r="B3" s="2"/>
+      <c r="C3" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="5"/>
+      <c r="D3" s="3"/>
     </row>
     <row r="4" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A4" s="39"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="7"/>
+      <c r="A4" s="35"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="5"/>
     </row>
     <row r="5" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A5" s="39"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="7"/>
+      <c r="A5" s="35"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="5"/>
     </row>
     <row r="6" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A6" s="39"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="41"/>
-      <c r="D6" s="7"/>
+      <c r="A6" s="35"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="37"/>
+      <c r="D6" s="5"/>
     </row>
     <row r="7" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A7" s="39"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="41"/>
-      <c r="D7" s="7"/>
+      <c r="A7" s="35"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="37"/>
+      <c r="D7" s="5"/>
     </row>
     <row r="8" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A8" s="39"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="41"/>
-      <c r="D8" s="7"/>
+      <c r="A8" s="35"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="5"/>
     </row>
     <row r="9" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A9" s="39"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="41"/>
-      <c r="D9" s="7"/>
+      <c r="A9" s="35"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="37"/>
+      <c r="D9" s="5"/>
     </row>
     <row r="10" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A10" s="39"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="41"/>
-      <c r="D10" s="7"/>
+      <c r="A10" s="35"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="37"/>
+      <c r="D10" s="5"/>
     </row>
     <row r="11" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A11" s="39"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="41"/>
-      <c r="D11" s="7"/>
+      <c r="A11" s="35"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="37"/>
+      <c r="D11" s="5"/>
     </row>
     <row r="12" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A12" s="39"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="41"/>
-      <c r="D12" s="7"/>
+      <c r="A12" s="35"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="37"/>
+      <c r="D12" s="5"/>
     </row>
     <row r="13" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A13" s="39"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="9"/>
+      <c r="A13" s="35"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="37"/>
+      <c r="D13" s="7"/>
     </row>
     <row r="14" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A14" s="39" t="s">
+      <c r="A14" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="B14" s="10"/>
-      <c r="C14" s="41" t="s">
+      <c r="B14" s="8"/>
+      <c r="C14" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="D14" s="11"/>
+      <c r="D14" s="9"/>
     </row>
     <row r="15" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A15" s="39"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="41"/>
-      <c r="D15" s="12"/>
+      <c r="A15" s="35"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="37"/>
+      <c r="D15" s="10"/>
     </row>
     <row r="16" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A16" s="39"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="12"/>
+      <c r="A16" s="35"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="37"/>
+      <c r="D16" s="10"/>
     </row>
     <row r="17" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A17" s="39"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="41"/>
-      <c r="D17" s="12"/>
+      <c r="A17" s="35"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="37"/>
+      <c r="D17" s="10"/>
     </row>
     <row r="18" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A18" s="39"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="41"/>
-      <c r="D18" s="12"/>
+      <c r="A18" s="35"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="37"/>
+      <c r="D18" s="10"/>
     </row>
     <row r="19" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A19" s="39"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="41"/>
-      <c r="D19" s="12"/>
+      <c r="A19" s="35"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="37"/>
+      <c r="D19" s="10"/>
     </row>
     <row r="20" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A20" s="39"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="41"/>
-      <c r="D20" s="12"/>
+      <c r="A20" s="35"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="37"/>
+      <c r="D20" s="10"/>
     </row>
     <row r="21" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A21" s="39"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="41"/>
-      <c r="D21" s="12"/>
+      <c r="A21" s="35"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="37"/>
+      <c r="D21" s="10"/>
     </row>
     <row r="22" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A22" s="39"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="41"/>
-      <c r="D22" s="12"/>
+      <c r="A22" s="35"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="37"/>
+      <c r="D22" s="10"/>
     </row>
     <row r="23" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A23" s="39"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="12"/>
+      <c r="A23" s="35"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="10"/>
     </row>
     <row r="24" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A24" s="39"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="41"/>
-      <c r="D24" s="13"/>
+      <c r="A24" s="35"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="37"/>
+      <c r="D24" s="11"/>
     </row>
     <row r="25" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A25" s="39" t="s">
+      <c r="A25" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="B25" s="14"/>
-      <c r="C25" s="41" t="s">
+      <c r="B25" s="12"/>
+      <c r="C25" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="D25" s="12"/>
+      <c r="D25" s="10"/>
     </row>
     <row r="26" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A26" s="39"/>
-      <c r="B26" s="15"/>
-      <c r="C26" s="41"/>
-      <c r="D26" s="12"/>
+      <c r="A26" s="35"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="37"/>
+      <c r="D26" s="10"/>
     </row>
     <row r="27" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A27" s="39"/>
-      <c r="B27" s="15"/>
-      <c r="C27" s="41"/>
-      <c r="D27" s="12"/>
+      <c r="A27" s="35"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="37"/>
+      <c r="D27" s="10"/>
     </row>
     <row r="28" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A28" s="39"/>
-      <c r="B28" s="15"/>
-      <c r="C28" s="41"/>
-      <c r="D28" s="12"/>
+      <c r="A28" s="35"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="37"/>
+      <c r="D28" s="10"/>
     </row>
     <row r="29" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A29" s="39"/>
-      <c r="B29" s="15"/>
-      <c r="C29" s="41"/>
-      <c r="D29" s="12"/>
+      <c r="A29" s="35"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="37"/>
+      <c r="D29" s="10"/>
     </row>
     <row r="30" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A30" s="39"/>
-      <c r="B30" s="15"/>
-      <c r="C30" s="41"/>
-      <c r="D30" s="12"/>
+      <c r="A30" s="35"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="37"/>
+      <c r="D30" s="10"/>
     </row>
     <row r="31" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A31" s="39"/>
-      <c r="B31" s="15"/>
-      <c r="C31" s="41"/>
-      <c r="D31" s="12"/>
+      <c r="A31" s="35"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="37"/>
+      <c r="D31" s="10"/>
     </row>
     <row r="32" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A32" s="39"/>
-      <c r="B32" s="15"/>
-      <c r="C32" s="41"/>
-      <c r="D32" s="12"/>
+      <c r="A32" s="35"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="37"/>
+      <c r="D32" s="10"/>
     </row>
     <row r="33" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A33" s="39"/>
-      <c r="B33" s="15"/>
-      <c r="C33" s="41"/>
-      <c r="D33" s="12"/>
+      <c r="A33" s="35"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="37"/>
+      <c r="D33" s="10"/>
     </row>
     <row r="34" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A34" s="39"/>
-      <c r="B34" s="15"/>
-      <c r="C34" s="41"/>
-      <c r="D34" s="12"/>
+      <c r="A34" s="35"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="37"/>
+      <c r="D34" s="10"/>
     </row>
     <row r="35" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A35" s="39"/>
-      <c r="B35" s="16"/>
-      <c r="C35" s="41"/>
-      <c r="D35" s="12"/>
+      <c r="A35" s="35"/>
+      <c r="B35" s="14"/>
+      <c r="C35" s="37"/>
+      <c r="D35" s="10"/>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="36"/>
-      <c r="B36" s="42" t="s">
+      <c r="A36" s="20"/>
+      <c r="B36" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="C36" s="44" t="s">
+      <c r="C36" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D36" s="45"/>
+      <c r="D36" s="25"/>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="36"/>
-      <c r="B37" s="43"/>
-      <c r="C37" s="46"/>
-      <c r="D37" s="47"/>
+      <c r="A37" s="20"/>
+      <c r="B37" s="23"/>
+      <c r="C37" s="26"/>
+      <c r="D37" s="27"/>
     </row>
     <row r="38" spans="1:4" ht="24" customHeight="1">
-      <c r="A38" s="36"/>
-      <c r="B38" s="17" t="s">
+      <c r="A38" s="20"/>
+      <c r="B38" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C38" s="48" t="s">
+      <c r="C38" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="D38" s="49"/>
+      <c r="D38" s="29"/>
     </row>
     <row r="39" spans="1:4" ht="24" customHeight="1">
-      <c r="A39" s="36"/>
-      <c r="B39" s="17" t="s">
+      <c r="A39" s="20"/>
+      <c r="B39" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C39" s="50"/>
-      <c r="D39" s="51"/>
+      <c r="C39" s="30"/>
+      <c r="D39" s="31"/>
     </row>
     <row r="40" spans="1:4" ht="24" customHeight="1">
-      <c r="A40" s="36"/>
-      <c r="B40" s="6"/>
-      <c r="C40" s="50" t="s">
+      <c r="A40" s="20"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="D40" s="51"/>
+      <c r="D40" s="31"/>
     </row>
     <row r="41" spans="1:4" ht="24.75" thickBot="1">
-      <c r="A41" s="37"/>
-      <c r="B41" s="18"/>
-      <c r="C41" s="52"/>
-      <c r="D41" s="53"/>
+      <c r="A41" s="21"/>
+      <c r="B41" s="16"/>
+      <c r="C41" s="32"/>
+      <c r="D41" s="33"/>
     </row>
     <row r="43" spans="1:4">
-      <c r="D43" s="3"/>
+      <c r="D43" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A36:A41"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:D37"/>
-    <mergeCell ref="C38:D39"/>
-    <mergeCell ref="C40:D41"/>
     <mergeCell ref="A3:A13"/>
     <mergeCell ref="C3:C13"/>
     <mergeCell ref="A14:A24"/>
     <mergeCell ref="C14:C24"/>
     <mergeCell ref="A25:A35"/>
     <mergeCell ref="C25:C35"/>
+    <mergeCell ref="A36:A41"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:D37"/>
+    <mergeCell ref="C38:D39"/>
+    <mergeCell ref="C40:D41"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.70866141732283472" right="0.31496062992125984" top="0.74803149606299213" bottom="0.55118110236220474" header="0.31496062992125984" footer="0.31496062992125984"/>
